--- a/artfynd/A 52999-2025 artfynd.xlsx
+++ b/artfynd/A 52999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,65 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6852080</v>
+        <v>55900957</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hult, 500 m NO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610570.4476992801</v>
+        <v>610570</v>
       </c>
       <c r="R2" t="n">
-        <v>6575100.392118</v>
+        <v>6575100</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,22 +747,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-07-10</t>
+          <t>2015-11-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-07-10</t>
+          <t>2015-11-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,52 +789,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112920450</v>
+        <v>6852080</v>
       </c>
       <c r="B3" t="n">
-        <v>104235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hult, 500 m NO, Srm</t>
@@ -884,17 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
+          <t>2013-07-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tre vinterståndare.</t>
+          <t>2013-07-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,7 +883,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,6 +898,121 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112920450</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hult, 500 m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>610570</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6575100</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Länna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tre vinterståndare.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bernt Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52999-2025 artfynd.xlsx
+++ b/artfynd/A 52999-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55900957</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6852080</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,8 +1028,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112920450</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>